--- a/results/reliability_eval/reliability_eval_typo-test-09-30/Llama-3-8B_P17_char_insert_noise_typo3_sample_tok25_temp0.1_direct_completion_rep5_beams5_maxent20_rows100_scores_typo-test-09-30.xlsx
+++ b/results/reliability_eval/reliability_eval_typo-test-09-30/Llama-3-8B_P17_char_insert_noise_typo3_sample_tok25_temp0.1_direct_completion_rep5_beams5_maxent20_rows100_scores_typo-test-09-30.xlsx
@@ -512,52 +512,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.9075</v>
+        <v>0.5304383116883117</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9639838161706765</v>
+        <v>0.5725474921903493</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1147546149725336</v>
+        <v>0.3550176625057949</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3278876846453712</v>
+        <v>9.303640534452819</v>
       </c>
       <c r="E2" t="n">
-        <v>25.48087953850683</v>
+        <v>21.04044401531266</v>
       </c>
       <c r="F2" t="n">
-        <v>0.715</v>
+        <v>0.4419642857142858</v>
       </c>
       <c r="G2" t="n">
-        <v>0.928778099387334</v>
+        <v>0.5406475453925152</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1835863927405244</v>
+        <v>0.4281265442692979</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6384434462963828</v>
+        <v>9.636884440254946</v>
       </c>
       <c r="J2" t="n">
-        <v>5.584204701362626</v>
+        <v>5.249111212807484</v>
       </c>
       <c r="K2" t="n">
-        <v>0.99375</v>
+        <v>0.9931006493506493</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9975919117647059</v>
+        <v>0.9912337662337662</v>
       </c>
       <c r="M2" t="n">
-        <v>0.024</v>
+        <v>0.028</v>
       </c>
       <c r="N2" t="n">
-        <v>0.06730116670092583</v>
+        <v>0.0836908257042818</v>
       </c>
       <c r="O2" t="n">
-        <v>4.854752960010435</v>
+        <v>4.786321532941346</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
